--- a/crates/unluminous-sheet/tests/fixtures/pages/pages-arial.xlsx
+++ b/crates/unluminous-sheet/tests/fixtures/pages/pages-arial.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\jason\dev\unluminous\.claude\worktrees\agent-afa636fef9f2b0676\crates\unluminous-sheet\tests\fixtures\pages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1928B898-D08B-48CD-B508-0423B3BC1630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3000507-C7B4-489B-8412-C7102EEC1778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1875" yWindow="6660" windowWidth="43200" windowHeight="23445" activeTab="6" xr2:uid="{456D406F-F78E-4901-8195-C0A63E351735}"/>
+    <workbookView xWindow="1875" yWindow="6660" windowWidth="43200" windowHeight="23445" activeTab="6" xr2:uid="{F177FAE0-55C8-4C09-9164-7084C517EC39}"/>
   </bookViews>
   <sheets>
     <sheet name="letter-p" sheetId="1" r:id="rId1"/>
@@ -412,7 +412,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20850F6F-D5EC-43EF-9688-D36F11F9C74E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F409C0BB-31BD-4345-AAD2-4B5036232685}">
   <dimension ref="A1:AN130"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -16283,7 +16283,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8D5A63B-3376-4923-B99E-FF3E89EC2FA4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEA04A7B-D09D-40F2-BA95-5A4E3EAE2F35}">
   <dimension ref="A1:AN130"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -32154,7 +32154,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AB1741-177C-4B42-BAF8-172441FD44A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69165A00-F8DD-4662-B2D6-80404935CD4C}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -48028,7 +48028,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3399E4F4-F7A1-435A-996C-E08FC687122C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88E06CB5-0608-4675-AA91-5258B331A4BA}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -63902,7 +63902,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2654A5C-54B3-4A14-9474-2FA2714AEC51}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E63C52C-E6AE-4AB3-9FD2-3EC8B8C92D3A}">
   <dimension ref="A1:AN130"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -79773,7 +79773,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1DE9D23-BB14-44B4-A841-37E7F1CAE26C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5348EF8-AC5E-48B4-AC39-B83ED7DA24D4}">
   <dimension ref="A1:AN130"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -95644,7 +95644,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E017C090-61B8-4DD2-AA15-913B9E3250CC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{932454E4-F741-40EF-B64C-903968B4EF64}">
   <dimension ref="A1:AN130"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
